--- a/kortdata/F_nätverkskort.xlsx
+++ b/kortdata/F_nätverkskort.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,8 +441,9 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,10 +479,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Stämning</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Beskrivning</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Antal exemplar</t>
         </is>
@@ -518,10 +524,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Du vet vem som fattar besluten och vilken dag de har tid för lunch.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>+1 på ett förhandlingsslag. Spelas före slaget.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -556,10 +567,15 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>Kalkylen är genomräknad två gånger. Motparten har inte ens läst bilagorna.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>+1 på ett förhandlingsslag. Spelas före slaget.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -594,10 +610,15 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Du vet vilken sida av gatan som får eftermiddagssol, och vad det är värt.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>+1 på ett förhandlingsslag. Spelas före slaget.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -632,10 +653,15 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>Budet landar samma dag som säljarens bokslut. Slumpen, förstås.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>+1 på ett förhandlingsslag. Spelas före slaget.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -670,10 +696,15 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>Ler, nickar och flyttar fram positionerna en halv procent i taget.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>+2 på ett förhandlingsslag. Spelas före slaget.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -708,10 +739,15 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>Timpriset får ekonomichefen att svettas. Motparten svettas mer.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>+2 på ett förhandlingsslag. Spelas före slaget.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -746,10 +782,15 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>Har förhandlat fram fler hyresavtal än de flesta har läst.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>+3 på ett förhandlingsslag. Spelas före slaget.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -780,10 +821,15 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>Pennan ligger redan på bordet när motparten kommer in i rummet.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>Vinn en förhandling automatiskt.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -814,10 +860,15 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>Ibland är det enklaste argumentet en siffra som ingen kan säga nej till.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>Vinn en förhandling automatiskt.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="I10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -848,10 +899,15 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>I den här branschen håller ett handslag fortfarande. Oftast.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>Vinn en förhandling automatiskt.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -886,10 +942,15 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>Tio centimeter extra på vinden. Ingen ser det, alla märker det.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>+1 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="I12" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -924,10 +985,15 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>En eftermiddag med ventilerna och huset slutar låta som en fabrik.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>+1 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -962,10 +1028,15 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>Kommer med mätare, grafer och en faktura som faktiskt är värd det.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1000,10 +1071,15 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>Har dragit mer rör än de flesta har sett, och vet var de brukar läcka.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1038,10 +1114,15 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>Någon läste det finstilta i Boverkets utlysning. Det lönade sig.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>+2 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1076,10 +1157,15 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>Certifikatet sitter på väggen. Resultatet sitter i elräkningen.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>+3 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1114,10 +1200,15 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>Från förstudie till injustering i ett paket, och ingen pekar på någon annan.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>+3 på ett energiuppgraderingsslag. Spelas efter slaget.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1148,10 +1239,15 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>Små saker som ingen ser, men som hyresgästerna slutar klaga på.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="I19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1182,10 +1278,15 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>Fastighetsskötaren byter packningar innan någon hunnit felanmäla.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="I20" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1216,10 +1317,15 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>Taket tvättas innan mossan hunnit bli ett problem.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="I21" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1250,10 +1356,15 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>Nya dörrar i trapphuset. Plötsligt vill alla bo just här.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="I22" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1284,10 +1395,15 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>Budgeten tålde det. Protokollet behöver inte veta detaljerna.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="I23" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1318,10 +1434,15 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>Tre lägenheter renoverade mellan två hyresgäster. Ingen märkte bullret.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="I24" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1352,10 +1473,15 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>Den som har skött huset i tjugo år vet precis var pengarna läcker.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="I25" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1386,10 +1512,15 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>Ingen dramatik, inga överraskningar. Bara ett hus som sköts.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>Lägg en dold +1 DN på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1420,10 +1551,15 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>Ett samtal till rätt person och ärendet försvann ur listan.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="I27" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1454,10 +1590,15 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>Jouren var på plats innan vattnet hann nå källaren.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1488,10 +1629,15 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>Någon tog tag i det som alla har gått förbi i ett halvår.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1522,10 +1668,15 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>Åtgärden var beställd innan revisorn hann skriva sin anmärkning.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="I30" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1556,10 +1707,15 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>Pressmeddelandet skrevs aldrig. Det behövdes inte.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
           <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1590,10 +1746,15 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>Pärmen med anmärkningar är tom. För första gången på länge.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>Ta bort ett minus- eller varningskort från en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="I32" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1624,10 +1785,15 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>Det stod i avtalet hela tiden. Någon hade bara glömt att läsa det.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="I33" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1658,10 +1824,15 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>Budgivaren fick ett bättre erbjudande att tänka på. Från dig.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1692,10 +1863,15 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>Avtalet är bundet i tio år, och nyckeln ligger hos er.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1726,10 +1902,15 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>Styrelsen har sammanträtt. Svaret är nej, och det är enhälligt.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1760,10 +1941,15 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>Servitutet från 1962 visade sig vara viktigare än någon trott.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>Avvärj ett fientligt bud på en av dina fastigheter.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="I37" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1794,10 +1980,15 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>Någon i branschen pratar för mycket på mingel. Tur att du lyssnade.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>Titta på ett dolt kort hos en motståndare.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="I38" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1828,10 +2019,15 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>Du har läst deras årsredovisning. Noggrannare än de själva.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>Titta på ett dolt kort hos en motståndare.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="I39" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1862,10 +2058,15 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>Hyresgästerna pratar i tvättstugan. Du har vänner i tvättstugan.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
           <t>Titta på ett dolt kort hos en motståndare.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1896,10 +2097,15 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>Ett mejl skickades till fel mottagare. Det var inte ditt fel.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>Titta på ett dolt kort hos en motståndare.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1930,10 +2136,15 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>Lite lägre hyra, lite bättre service, och flyttlasset går åt ert håll.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>En hyresgäst hos en konkurrent flyttar till er efter ett bättre erbjudande. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1964,10 +2175,15 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>Butikskedjan behöver ett nytt hem. Ni hade ett.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>Er uthyrare vinner en stor hyresgäst som konkurrenten räknat med. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="I43" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1998,10 +2214,15 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>Tre månader hyresfritt och flytthjälp. Svårt att säga nej till.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>Tre månaders rabatt räcker för att hyresgästen byter hyresvärd. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="I44" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2032,10 +2253,15 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>Fixat samma dag slår "vi återkommer" varje gång.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
           <t>Hyresgästen tröttnar på konkurrentens service och flyttar till er. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2066,10 +2292,15 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>Samma pris, men utsikt mot vattnet i stället för mot parkeringen.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>Er fastighet erbjuder mer för pengarna och hyresgästen byter. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="I46" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2100,10 +2331,15 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>Nya ytor, ny planlösning och en hyresgäst som gärna byter adress.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
           <t>Ni erbjuder en anpassad yta som konkurrenten inte kan matcha. Kräver att du äger en fastighet av samma typ som motspelarens. Lägg en dold plusbricka på din och en dold minusbricka på motspelarens.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="I47" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2134,10 +2370,15 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>Ett bättre erbjudande, en tjänstebil och ett hörnrum. Svaret blev ja.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
           <t>En nyckelperson hos en konkurrent tackar ja till ert erbjudande. Ta ett slumpvis nätverkskort från en motspelares hand.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2168,10 +2409,15 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>Konsulten har bytt uppdragsgivare och tog med sig anteckningarna.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
           <t>Konkurrentens konsult går över till er mitt i uppdraget. Ta ett slumpvis nätverkskort från en motspelares hand.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="I49" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2202,10 +2448,15 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
+          <t>Headhuntern hittade rätt person. Hos konkurrenten, förstås.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
           <t>Headhuntern hittar exakt den person ni behöver — hos en konkurrent. Ta ett slumpvis nätverkskort från en motspelares hand.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="I50" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2236,10 +2487,15 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>Visitkortet från mässan visade sig vara värt mer än mässan.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
           <t>Dra ett nätverkskort.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="I51" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2270,10 +2526,15 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>"Ring henne, säg att jag skickade dig." Det räckte.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
           <t>Dra ett nätverkskort.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="I52" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2304,10 +2565,15 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>Vin, mingel och en affärsidé skriven på en servett.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>Dra ett nätverkskort.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2338,10 +2604,15 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>Ni gick samma utbildning för femton år sedan. Nu har hen ett förslag.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>Dra ett nätverkskort.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="I54" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2372,10 +2643,15 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
+          <t>Det bästa tipset den här veckan kom med en pappmugg i handen.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
           <t>Dra ett nätverkskort.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="I55" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2406,10 +2682,15 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>Kalkylen har en rad som heter "oförutsett". Den är inte tom.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
           <t>Ta en riskbuffert.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="I56" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2440,10 +2721,15 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>Pengarna sattes av innan någon behövde dem. Det är hela poängen.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
           <t>Ta en riskbuffert.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="I57" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2474,10 +2760,15 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
+          <t>Pessimisten i styrelsen fick rätt, och ni var förberedda.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
           <t>Ta en riskbuffert.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="I58" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2508,10 +2799,15 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>Ägarna sköt till, med en tydlig förväntan om att slippa göra om det.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
           <t>Ta en riskbuffert.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="I59" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2542,10 +2838,15 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>Tre dagar på kursgård. Förvaltarna kom tillbaka med en plan.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
           <t>FC eller FS går en intern ledarutbildning. Lägg en utvecklingsbricka på din FC eller FS.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="I60" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2576,10 +2877,15 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>Diplomet hänger i receptionen och hyresgästerna har lagt märke till det.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
           <t>Er förvaltningschef tar en eftertraktad certifiering. Lägg en utvecklingsbricka på din FC eller FS.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="I61" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2610,10 +2916,15 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>Den erfarna delar med sig, så att den nya slipper göra samma misstag.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>Erfaren kollega delar med sig av sina knep. Lägg en utvecklingsbricka på din FC eller FS.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2644,10 +2955,15 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>Radiatorerna är varma i hela huset. Samtidigt. För första gången.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
           <t>Värmen balanseras om och radiatorerna slutar gå för fullt. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2678,10 +2994,15 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
+          <t>Taket ger el i stället för bara skugga.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
           <t>Taket får solceller som täcker en del av fastighetselen. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2712,10 +3033,15 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
+          <t>Trettio centimeter lösull och vinden slutar vara husets största läcka.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
           <t>Vindsbjälklaget isoleras och värmeförlusten minskar. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="I65" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2746,10 +3072,15 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>Trapphusen lyser upp när någon kommer och släcks när de går.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
           <t>Trapphus och garage får ny belysning med närvarostyrning. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="I66" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2780,10 +3111,15 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
+          <t>Värmen i frånluften går inte längre rakt ut genom taket.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
           <t>Värmen i frånluften tas tillvara i stället för att blåsa ut. Lägg en dold energiplusbricka på en egen fastighet.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="I67" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2814,10 +3150,15 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
+          <t>Hyresgästföreningen och bolaget blev överens. Före lunch.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
           <t>Ett nytt avtal höjer hyresnivån på en hel fastighet. +1 DN direkt och permanent på en egen fastighet.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="I68" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2852,10 +3193,15 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
+          <t>Kvartalsrapporten var inte vacker. De tar det ni bjuder.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
           <t>Ditt tvångsbud kostar 1,1 × MV i stället för 1,2 × MV. Spelas när du lägger budet.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="I69" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2890,10 +3236,15 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
+          <t>Siffrorna säger vad fastigheten är värd. Känslor kostar extra.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
           <t>Ditt tvångsbud kostar 1,1 × MV i stället för 1,2 × MV. Spelas när du lägger budet.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2928,10 +3279,15 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
+          <t>Banken ringer dem varje dag. Ni ringer en gång, med ett bud.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
           <t>Ditt tvångsbud kostar 1,1 × MV i stället för 1,2 × MV. Spelas när du lägger budet.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="I71" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2962,10 +3318,15 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
+          <t>Tre advokater, två ombud och en ursäktande notis i Dagens Industri.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
           <t>Ditt tvångsbud kan inte stoppas — varken med stoppkort eller riskbuffertar. Spelas när du lägger budet.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="I72" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2996,10 +3357,15 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
+          <t>Rösterna var räknade innan stämman ens började.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
           <t>Ditt tvångsbud kan inte stoppas — varken med stoppkort eller riskbuffertar. Spelas när du lägger budet.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="I73" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3030,10 +3396,15 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
+          <t>Totalentreprenören lämnade över nycklarna och en garanti på fem år.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
           <t>Höj energiklassen ett steg på en egen fastighet — utan slag och utan kostnad.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="I74" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3064,10 +3435,15 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
+          <t>Oljepannan åker ut, fjärrvärmen kommer in. Energibolaget står för det mesta.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
           <t>Höj energiklassen ett steg på en egen fastighet — utan slag och utan kostnad.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="I75" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3098,10 +3474,15 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
+          <t>Energibolaget behöver ett referensprojekt. Ni har ett hus.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
           <t>Höj energiklassen ett steg på en egen fastighet — utan slag och utan kostnad.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3136,10 +3517,15 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
+          <t>Den nya banken ville ha affären. Mer än den gamla ville behålla den.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
           <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
         </is>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="I77" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3174,10 +3560,15 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
+          <t>Hållbarhetsrapporten gav en grön stämpel, och stämpeln gav lägre ränta.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
           <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="I78" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3212,10 +3603,15 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
+          <t>Någon band räntan dagen innan Riksbanken höjde. Ingen minns vem.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
           <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
         </is>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="I79" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3246,10 +3642,15 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
+          <t>Besiktningsmannen tittade under golvmattan. Det gör inte alla.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
           <t>När du köper en fastighet (även tvångsköp): dra två DD-kort och välj vilket som gäller.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="I80" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3280,10 +3681,15 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
+          <t>Ett helt team gick igenom handlingarna. Ni vet vad ni köper.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
           <t>När du köper en fastighet (även tvångsköp): dra två DD-kort och välj vilket som gäller.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="I81" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3318,10 +3724,15 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
+          <t>Kontoret stod halvtomt. Nu står det kö till lägenheterna.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
           <t>Betala 5 Mkr: en egen lokal eller ett eget kontor byggs om till hyresrätt och följer bostadsspåret i yieldbanan. DN och energiklass behålls.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="I82" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3352,10 +3763,15 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
+          <t>Ni ville köpa oss? Då köper vi er först.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
           <t>Stoppa ett tvångsbud mot dig. Du får dessutom köpa en av budgivarens fastigheter till 1,0 × MV (valfritt).</t>
         </is>
       </c>
-      <c r="H83" s="2" t="n">
+      <c r="I83" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3386,10 +3802,15 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
+          <t>Det bästa försvaret är ett anfall, gärna mot budgivarens bästa hus.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
           <t>Stoppa ett tvångsbud mot dig. Du får dessutom köpa en av budgivarens fastigheter till 1,0 × MV (valfritt).</t>
         </is>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="I84" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4721,7 +5142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4887,12 +5308,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beskrivning</t>
+          <t>Stämning</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Beskrivning</t>
+          <t>Stämning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4909,20 +5330,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Beskrivning</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Beskrivning</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Korttext</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Antal exemplar</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Per spel</t>
         </is>

--- a/kortdata/F_nätverkskort.xlsx
+++ b/kortdata/F_nätverkskort.xlsx
@@ -3323,7 +3323,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Ditt tvångsbud kan inte stoppas — varken med stoppkort eller riskbuffertar. Spelas när du lägger budet.</t>
+          <t>Ditt tvångsbud kan inte stoppas och ingen duell slås: köpet går igenom. Spelas när du lägger budet.</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Ditt tvångsbud kan inte stoppas — varken med stoppkort eller riskbuffertar. Spelas när du lägger budet.</t>
+          <t>Ditt tvångsbud kan inte stoppas och ingen duell slås: köpet går igenom. Spelas när du lägger budet.</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">

--- a/kortdata/F_nätverkskort.xlsx
+++ b/kortdata/F_nätverkskort.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3695,41 +3695,37 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>PK-81</t>
+          <t>PK-82</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>konvertering</t>
+          <t>motbud</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>nar_som_helst</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>reaktivt</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Kontor blir bostäder</t>
+          <t>Motbud — vi köper er i stället</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Kontoret stod halvtomt. Nu står det kö till lägenheterna.</t>
+          <t>Ni ville köpa oss? Då köper vi er först.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Betala 5 Mkr: en egen lokal eller ett eget kontor byggs om till hyresrätt och följer bostadsspåret i yieldbanan. DN och energiklass behålls.</t>
+          <t>Stoppa ett tvångsbud mot dig. Du får dessutom köpa en av budgivarens fastigheter till 1,0 × MV (valfritt).</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -3738,11 +3734,11 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>PK-82</t>
+          <t>PK-83</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3758,12 +3754,12 @@
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Motbud — vi köper er i stället</t>
+          <t>Pac-Man-försvaret</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Ni ville köpa oss? Då köper vi er först.</t>
+          <t>Det bästa försvaret är ett anfall, gärna mot budgivarens bästa hus.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3772,45 +3768,6 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>PK-83</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>motbud</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>reaktivt</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Pac-Man-försvaret</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Det bästa försvaret är ett anfall, gärna mot budgivarens bästa hus.</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Stoppa ett tvångsbud mot dig. Du får dessutom köpa en av budgivarens fastigheter till 1,0 × MV (valfritt).</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3861,7 +3818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5088,11 +5045,11 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kontor blir bostäder</t>
+          <t>Motbud — vi köper er i stället</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5103,29 +5060,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Motbud — vi köper er i stället</t>
+          <t>Pac-Man-försvaret</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
-        <is>
-          <t>ej bestämt</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Pac-Man-försvaret</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
         <is>
           <t>ej bestämt</t>
         </is>
@@ -5421,7 +5363,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>83 (kortspecen: 83)</t>
+          <t>82 (kortspecen: 83; PK-81 Kontor blir bostäder borttaget 2026-09-27 – inga kort kostar pengar)</t>
         </is>
       </c>
     </row>

--- a/kortdata/F_nätverkskort.xlsx
+++ b/kortdata/F_nätverkskort.xlsx
@@ -3497,7 +3497,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>omforhandlat_lan</t>
+          <t>direkt_dn_plus_egen</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3505,11 +3505,7 @@
           <t>nar_som_helst</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Ny bank lockar</t>
@@ -3522,7 +3518,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
+          <t>+1 driftnetto direkt och permanent på en egen fastighet.</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
@@ -3540,7 +3536,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>omforhandlat_lan</t>
+          <t>direkt_dn_plus_egen</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3548,11 +3544,7 @@
           <t>nar_som_helst</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="E78" s="2" t="n"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Grön obligation</t>
@@ -3565,7 +3557,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
+          <t>+1 driftnetto direkt och permanent på en egen fastighet.</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
@@ -3583,7 +3575,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>omforhandlat_lan</t>
+          <t>direkt_dn_plus_egen</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3591,11 +3583,7 @@
           <t>nar_som_helst</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="E79" s="2" t="n"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Räntebindning i rätt läge</t>
@@ -3608,7 +3596,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Sänk räntan på en egen fastighet med 1 Mkr/år för resten av spelet (DN +1, marknadsvärdet oförändrat).</t>
+          <t>+1 driftnetto direkt och permanent på en egen fastighet.</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
